--- a/xlsx/tests/templates/yearly_calendar.xlsx
+++ b/xlsx/tests/templates/yearly_calendar.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dg-ac/Documents/IronCalc Mkt/Templates/final/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F690FD88-B6F3-944C-8A95-B6E9812000F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E02E46D9-EFAE-9744-B9A0-DAB4517D2AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="-19400" windowWidth="33960" windowHeight="17260" xr2:uid="{6F0581DF-A6A1-8847-8CD1-D7A1DAEC65B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Yearly calendar" sheetId="1" r:id="rId1"/>
+    <sheet name="METADATA" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="cal_month">_xlfn.LAMBDA(_xlpm.mo,_xlfn.LET(_xlpm.anchor,DATE(cal_year,_xlpm.mo,1),_xlpm.first_mon,_xlpm.anchor-(WEEKDAY(_xlpm.anchor,2)-1),_xlpm.grid,_xlfn.SEQUENCE(6,7,0),_xlpm.d,_xlpm.first_mon+_xlpm.grid,IF(MONTH(_xlpm.d)=_xlpm.mo,DAY(_xlpm.d),"")))</definedName>
@@ -22,7 +23,6 @@
     <definedName name="week">_xlfn.LAMBDA(LEFT(TEXT(2+_xlfn.SEQUENCE(1,7,0),"ddd")))</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -65,6 +65,14 @@
     </bk>
   </cellMetadata>
 </metadata>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t>NOW</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -170,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -206,177 +214,12 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="31">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF26800"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF26800"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF26800"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF26800"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF26800"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF26800"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF26800"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF26800"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF26800"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF26800"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF26800"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF26800"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3685,65 +3528,87 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B6:H11">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>AND(ISNUMBER(B6),B6=DAY(TODAY()),1=MONTH(TODAY()),$B$2=YEAR(TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B15:H20">
+    <cfRule type="expression" dxfId="10" priority="5">
+      <formula>AND(ISNUMBER(B15),B15=DAY(TODAY()),5=MONTH(TODAY()),$B$2=YEAR(TODAY()))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24:H29">
+    <cfRule type="expression" dxfId="9" priority="9">
+      <formula>AND(ISNUMBER(B24),B24=DAY(TODAY()),9=MONTH(TODAY()),$B$2=YEAR(TODAY()))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J6:P11">
-    <cfRule type="expression" dxfId="29" priority="2">
+    <cfRule type="expression" dxfId="8" priority="2">
       <formula>AND(ISNUMBER(J6),J6=DAY(TODAY()),2=MONTH(TODAY()),$B$2=YEAR(TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J15:P20">
+    <cfRule type="expression" dxfId="7" priority="6">
+      <formula>AND(ISNUMBER(J15),J15=DAY(TODAY()),6=MONTH(TODAY()),$B$2=YEAR(TODAY()))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J24:P29">
+    <cfRule type="expression" dxfId="6" priority="10">
+      <formula>AND(ISNUMBER(J24),J24=DAY(TODAY()),10=MONTH(TODAY()),$B$2=YEAR(TODAY()))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="R6:X11">
-    <cfRule type="expression" dxfId="28" priority="3">
+    <cfRule type="expression" dxfId="5" priority="3">
       <formula>AND(ISNUMBER(R6),R6=DAY(TODAY()),3=MONTH(TODAY()),$B$2=YEAR(TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="R15:X20">
+    <cfRule type="expression" dxfId="4" priority="7">
+      <formula>AND(ISNUMBER(R15),R15=DAY(TODAY()),7=MONTH(TODAY()),$B$2=YEAR(TODAY()))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R24:X29">
+    <cfRule type="expression" dxfId="3" priority="11">
+      <formula>AND(ISNUMBER(R24),R24=DAY(TODAY()),11=MONTH(TODAY()),$B$2=YEAR(TODAY()))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="Z6:AF11">
-    <cfRule type="expression" dxfId="27" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>AND(ISNUMBER(Z6),Z6=DAY(TODAY()),4=MONTH(TODAY()),$B$2=YEAR(TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B15:H20">
-    <cfRule type="expression" dxfId="26" priority="5">
-      <formula>AND(ISNUMBER(B15),B15=DAY(TODAY()),5=MONTH(TODAY()),$B$2=YEAR(TODAY()))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J15:P20">
-    <cfRule type="expression" dxfId="25" priority="6">
-      <formula>AND(ISNUMBER(J15),J15=DAY(TODAY()),6=MONTH(TODAY()),$B$2=YEAR(TODAY()))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R15:X20">
-    <cfRule type="expression" dxfId="24" priority="7">
-      <formula>AND(ISNUMBER(R15),R15=DAY(TODAY()),7=MONTH(TODAY()),$B$2=YEAR(TODAY()))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="Z15:AF20">
-    <cfRule type="expression" dxfId="23" priority="8">
+    <cfRule type="expression" dxfId="1" priority="8">
       <formula>AND(ISNUMBER(Z15),Z15=DAY(TODAY()),8=MONTH(TODAY()),$B$2=YEAR(TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B24:H29">
-    <cfRule type="expression" dxfId="22" priority="9">
-      <formula>AND(ISNUMBER(B24),B24=DAY(TODAY()),9=MONTH(TODAY()),$B$2=YEAR(TODAY()))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J24:P29">
-    <cfRule type="expression" dxfId="21" priority="10">
-      <formula>AND(ISNUMBER(J24),J24=DAY(TODAY()),10=MONTH(TODAY()),$B$2=YEAR(TODAY()))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R24:X29">
-    <cfRule type="expression" dxfId="20" priority="11">
-      <formula>AND(ISNUMBER(R24),R24=DAY(TODAY()),11=MONTH(TODAY()),$B$2=YEAR(TODAY()))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="Z24:AF29">
-    <cfRule type="expression" dxfId="19" priority="12">
+    <cfRule type="expression" dxfId="0" priority="12">
       <formula>AND(ISNUMBER(Z24),Z24=DAY(TODAY()),12=MONTH(TODAY()),$B$2=YEAR(TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC482F56-AD01-2740-A8C0-FDE74307E449}">
+  <dimension ref="A2:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="13">
+        <f ca="1">NOW()</f>
+        <v>46226.525753009257</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/xlsx/tests/templates/yearly_calendar.xlsx
+++ b/xlsx/tests/templates/yearly_calendar.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dg-ac/Documents/IronCalc Mkt/Templates/final/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dg-ac/Documents/IronCalc Mkt/Templates/v0.8.02/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E02E46D9-EFAE-9744-B9A0-DAB4517D2AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88D010F-C510-4B4C-B6B5-F84C4CC698E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="-19400" windowWidth="33960" windowHeight="17260" xr2:uid="{6F0581DF-A6A1-8847-8CD1-D7A1DAEC65B8}"/>
   </bookViews>
@@ -831,119 +831,95 @@
     </row>
     <row r="5" spans="1:33" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
-      <c r="B5" s="2" t="str">
-        <f>LEFT(TEXT(DATE(2024,1,1)+COLUMN()-COLUMN($B$5),"dddd"),1)</f>
+      <c r="B5" s="2" t="str" cm="1">
+        <f t="array" ref="B5:H5">week()</f>
         <v>M</v>
       </c>
       <c r="C5" s="2" t="str">
-        <f t="shared" ref="C5:H5" si="0">LEFT(TEXT(DATE(2024,1,1)+COLUMN()-COLUMN($B$5),"dddd"),1)</f>
         <v>T</v>
       </c>
       <c r="D5" s="2" t="str">
-        <f t="shared" si="0"/>
         <v>W</v>
       </c>
       <c r="E5" s="2" t="str">
-        <f t="shared" si="0"/>
         <v>T</v>
       </c>
       <c r="F5" s="2" t="str">
-        <f t="shared" si="0"/>
         <v>F</v>
       </c>
       <c r="G5" s="12" t="str">
-        <f t="shared" si="0"/>
         <v>S</v>
       </c>
       <c r="H5" s="12" t="str">
-        <f t="shared" si="0"/>
         <v>S</v>
       </c>
       <c r="I5" s="11"/>
-      <c r="J5" s="2" t="str">
-        <f>LEFT(TEXT(DATE(2024,1,1)+COLUMN()-COLUMN($J$5),"dddd"),1)</f>
+      <c r="J5" s="2" t="str" cm="1">
+        <f t="array" ref="J5:P5">week()</f>
         <v>M</v>
       </c>
       <c r="K5" s="2" t="str">
-        <f t="shared" ref="K5:P5" si="1">LEFT(TEXT(DATE(2024,1,1)+COLUMN()-COLUMN($J$5),"dddd"),1)</f>
         <v>T</v>
       </c>
       <c r="L5" s="2" t="str">
-        <f t="shared" si="1"/>
         <v>W</v>
       </c>
       <c r="M5" s="2" t="str">
-        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="N5" s="2" t="str">
-        <f t="shared" si="1"/>
         <v>F</v>
       </c>
       <c r="O5" s="12" t="str">
-        <f t="shared" si="1"/>
         <v>S</v>
       </c>
       <c r="P5" s="12" t="str">
-        <f t="shared" si="1"/>
         <v>S</v>
       </c>
       <c r="Q5" s="11"/>
-      <c r="R5" s="2" t="str">
-        <f>LEFT(TEXT(DATE(2024,1,1)+COLUMN()-COLUMN($R$5),"dddd"),1)</f>
+      <c r="R5" s="2" t="str" cm="1">
+        <f t="array" ref="R5:X5">week()</f>
         <v>M</v>
       </c>
       <c r="S5" s="2" t="str">
-        <f t="shared" ref="S5:X5" si="2">LEFT(TEXT(DATE(2024,1,1)+COLUMN()-COLUMN($R$5),"dddd"),1)</f>
         <v>T</v>
       </c>
       <c r="T5" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>W</v>
       </c>
       <c r="U5" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>T</v>
       </c>
       <c r="V5" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>F</v>
       </c>
       <c r="W5" s="12" t="str">
-        <f t="shared" si="2"/>
         <v>S</v>
       </c>
       <c r="X5" s="12" t="str">
-        <f t="shared" si="2"/>
         <v>S</v>
       </c>
       <c r="Y5" s="11"/>
-      <c r="Z5" s="2" t="str">
-        <f>LEFT(TEXT(DATE(2024,1,1)+COLUMN()-COLUMN($Z$5),"dddd"),1)</f>
+      <c r="Z5" s="2" t="str" cm="1">
+        <f t="array" ref="Z5:AF5">week()</f>
         <v>M</v>
       </c>
       <c r="AA5" s="2" t="str">
-        <f t="shared" ref="AA5:AF5" si="3">LEFT(TEXT(DATE(2024,1,1)+COLUMN()-COLUMN($Z$5),"dddd"),1)</f>
         <v>T</v>
       </c>
       <c r="AB5" s="2" t="str">
-        <f t="shared" si="3"/>
         <v>W</v>
       </c>
       <c r="AC5" s="2" t="str">
-        <f t="shared" si="3"/>
         <v>T</v>
       </c>
       <c r="AD5" s="2" t="str">
-        <f t="shared" si="3"/>
         <v>F</v>
       </c>
       <c r="AE5" s="12" t="str">
-        <f t="shared" si="3"/>
         <v>S</v>
       </c>
       <c r="AF5" s="12" t="str">
-        <f t="shared" si="3"/>
         <v>S</v>
       </c>
       <c r="AG5" s="9"/>
@@ -1746,119 +1722,95 @@
     </row>
     <row r="14" spans="1:33" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
-      <c r="B14" s="2" t="str">
-        <f>LEFT(TEXT(DATE(2024,1,1)+COLUMN()-COLUMN($B$14),"dddd"),1)</f>
+      <c r="B14" s="2" t="str" cm="1">
+        <f t="array" ref="B14:H14">week()</f>
         <v>M</v>
       </c>
       <c r="C14" s="2" t="str">
-        <f t="shared" ref="C14:H14" si="4">LEFT(TEXT(DATE(2024,1,1)+COLUMN()-COLUMN($B$14),"dddd"),1)</f>
         <v>T</v>
       </c>
       <c r="D14" s="2" t="str">
-        <f t="shared" si="4"/>
         <v>W</v>
       </c>
       <c r="E14" s="2" t="str">
-        <f t="shared" si="4"/>
         <v>T</v>
       </c>
       <c r="F14" s="2" t="str">
-        <f t="shared" si="4"/>
         <v>F</v>
       </c>
       <c r="G14" s="12" t="str">
-        <f t="shared" si="4"/>
         <v>S</v>
       </c>
       <c r="H14" s="12" t="str">
-        <f t="shared" si="4"/>
         <v>S</v>
       </c>
       <c r="I14" s="11"/>
-      <c r="J14" s="2" t="str">
-        <f>LEFT(TEXT(DATE(2024,1,1)+COLUMN()-COLUMN($J$14),"dddd"),1)</f>
+      <c r="J14" s="2" t="str" cm="1">
+        <f t="array" ref="J14:P14">week()</f>
         <v>M</v>
       </c>
       <c r="K14" s="2" t="str">
-        <f t="shared" ref="K14:P14" si="5">LEFT(TEXT(DATE(2024,1,1)+COLUMN()-COLUMN($J$14),"dddd"),1)</f>
         <v>T</v>
       </c>
       <c r="L14" s="2" t="str">
-        <f t="shared" si="5"/>
         <v>W</v>
       </c>
       <c r="M14" s="2" t="str">
-        <f t="shared" si="5"/>
         <v>T</v>
       </c>
       <c r="N14" s="2" t="str">
-        <f t="shared" si="5"/>
         <v>F</v>
       </c>
       <c r="O14" s="12" t="str">
-        <f t="shared" si="5"/>
         <v>S</v>
       </c>
       <c r="P14" s="12" t="str">
-        <f t="shared" si="5"/>
         <v>S</v>
       </c>
       <c r="Q14" s="11"/>
-      <c r="R14" s="2" t="str">
-        <f>LEFT(TEXT(DATE(2024,1,1)+COLUMN()-COLUMN($R$14),"dddd"),1)</f>
+      <c r="R14" s="2" t="str" cm="1">
+        <f t="array" ref="R14:X14">week()</f>
         <v>M</v>
       </c>
       <c r="S14" s="2" t="str">
-        <f t="shared" ref="S14:X14" si="6">LEFT(TEXT(DATE(2024,1,1)+COLUMN()-COLUMN($R$14),"dddd"),1)</f>
         <v>T</v>
       </c>
       <c r="T14" s="2" t="str">
-        <f t="shared" si="6"/>
         <v>W</v>
       </c>
       <c r="U14" s="2" t="str">
-        <f t="shared" si="6"/>
         <v>T</v>
       </c>
       <c r="V14" s="2" t="str">
-        <f t="shared" si="6"/>
         <v>F</v>
       </c>
       <c r="W14" s="12" t="str">
-        <f t="shared" si="6"/>
         <v>S</v>
       </c>
       <c r="X14" s="12" t="str">
-        <f t="shared" si="6"/>
         <v>S</v>
       </c>
       <c r="Y14" s="11"/>
-      <c r="Z14" s="2" t="str">
-        <f>LEFT(TEXT(DATE(2024,1,1)+COLUMN()-COLUMN($Z$14),"dddd"),1)</f>
+      <c r="Z14" s="2" t="str" cm="1">
+        <f t="array" ref="Z14:AF14">week()</f>
         <v>M</v>
       </c>
       <c r="AA14" s="2" t="str">
-        <f t="shared" ref="AA14:AF14" si="7">LEFT(TEXT(DATE(2024,1,1)+COLUMN()-COLUMN($Z$14),"dddd"),1)</f>
         <v>T</v>
       </c>
       <c r="AB14" s="2" t="str">
-        <f t="shared" si="7"/>
         <v>W</v>
       </c>
       <c r="AC14" s="2" t="str">
-        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="AD14" s="2" t="str">
-        <f t="shared" si="7"/>
         <v>F</v>
       </c>
       <c r="AE14" s="12" t="str">
-        <f t="shared" si="7"/>
         <v>S</v>
       </c>
       <c r="AF14" s="12" t="str">
-        <f t="shared" si="7"/>
         <v>S</v>
       </c>
       <c r="AG14" s="9"/>
@@ -2660,119 +2612,95 @@
     </row>
     <row r="23" spans="1:33" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
-      <c r="B23" s="2" t="str">
-        <f>LEFT(TEXT(DATE(2024,1,1)+COLUMN()-COLUMN($B$23),"dddd"),1)</f>
+      <c r="B23" s="2" t="str" cm="1">
+        <f t="array" ref="B23:H23">week()</f>
         <v>M</v>
       </c>
       <c r="C23" s="2" t="str">
-        <f t="shared" ref="C23:H23" si="8">LEFT(TEXT(DATE(2024,1,1)+COLUMN()-COLUMN($B$23),"dddd"),1)</f>
         <v>T</v>
       </c>
       <c r="D23" s="2" t="str">
-        <f t="shared" si="8"/>
         <v>W</v>
       </c>
       <c r="E23" s="2" t="str">
-        <f t="shared" si="8"/>
         <v>T</v>
       </c>
       <c r="F23" s="2" t="str">
-        <f t="shared" si="8"/>
         <v>F</v>
       </c>
       <c r="G23" s="12" t="str">
-        <f t="shared" si="8"/>
         <v>S</v>
       </c>
       <c r="H23" s="12" t="str">
-        <f t="shared" si="8"/>
         <v>S</v>
       </c>
       <c r="I23" s="11"/>
-      <c r="J23" s="2" t="str">
-        <f>LEFT(TEXT(DATE(2024,1,1)+COLUMN()-COLUMN($J$23),"dddd"),1)</f>
+      <c r="J23" s="2" t="str" cm="1">
+        <f t="array" ref="J23:P23">week()</f>
         <v>M</v>
       </c>
       <c r="K23" s="2" t="str">
-        <f t="shared" ref="K23:P23" si="9">LEFT(TEXT(DATE(2024,1,1)+COLUMN()-COLUMN($J$23),"dddd"),1)</f>
         <v>T</v>
       </c>
       <c r="L23" s="2" t="str">
-        <f t="shared" si="9"/>
         <v>W</v>
       </c>
       <c r="M23" s="2" t="str">
-        <f t="shared" si="9"/>
         <v>T</v>
       </c>
       <c r="N23" s="2" t="str">
-        <f t="shared" si="9"/>
         <v>F</v>
       </c>
       <c r="O23" s="12" t="str">
-        <f t="shared" si="9"/>
         <v>S</v>
       </c>
       <c r="P23" s="12" t="str">
-        <f t="shared" si="9"/>
         <v>S</v>
       </c>
       <c r="Q23" s="11"/>
-      <c r="R23" s="2" t="str">
-        <f>LEFT(TEXT(DATE(2024,1,1)+COLUMN()-COLUMN($R$23),"dddd"),1)</f>
+      <c r="R23" s="2" t="str" cm="1">
+        <f t="array" ref="R23:X23">week()</f>
         <v>M</v>
       </c>
       <c r="S23" s="2" t="str">
-        <f t="shared" ref="S23:X23" si="10">LEFT(TEXT(DATE(2024,1,1)+COLUMN()-COLUMN($R$23),"dddd"),1)</f>
         <v>T</v>
       </c>
       <c r="T23" s="2" t="str">
-        <f t="shared" si="10"/>
         <v>W</v>
       </c>
       <c r="U23" s="2" t="str">
-        <f t="shared" si="10"/>
         <v>T</v>
       </c>
       <c r="V23" s="2" t="str">
-        <f t="shared" si="10"/>
         <v>F</v>
       </c>
       <c r="W23" s="12" t="str">
-        <f t="shared" si="10"/>
         <v>S</v>
       </c>
       <c r="X23" s="12" t="str">
-        <f t="shared" si="10"/>
         <v>S</v>
       </c>
       <c r="Y23" s="11"/>
-      <c r="Z23" s="2" t="str">
-        <f>LEFT(TEXT(DATE(2024,1,1)+COLUMN()-COLUMN($Z$23),"dddd"),1)</f>
+      <c r="Z23" s="2" t="str" cm="1">
+        <f t="array" ref="Z23:AF23">week()</f>
         <v>M</v>
       </c>
       <c r="AA23" s="2" t="str">
-        <f t="shared" ref="AA23:AF23" si="11">LEFT(TEXT(DATE(2024,1,1)+COLUMN()-COLUMN($Z$23),"dddd"),1)</f>
         <v>T</v>
       </c>
       <c r="AB23" s="2" t="str">
-        <f t="shared" si="11"/>
         <v>W</v>
       </c>
       <c r="AC23" s="2" t="str">
-        <f t="shared" si="11"/>
         <v>T</v>
       </c>
       <c r="AD23" s="2" t="str">
-        <f t="shared" si="11"/>
         <v>F</v>
       </c>
       <c r="AE23" s="12" t="str">
-        <f t="shared" si="11"/>
         <v>S</v>
       </c>
       <c r="AF23" s="12" t="str">
-        <f t="shared" si="11"/>
         <v>S</v>
       </c>
       <c r="AG23" s="9"/>
@@ -3605,7 +3533,7 @@
       </c>
       <c r="B2" s="13">
         <f ca="1">NOW()</f>
-        <v>46226.525753009257</v>
+        <v>46233.603531944442</v>
       </c>
     </row>
   </sheetData>
